--- a/Profile_List.xlsx
+++ b/Profile_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\675939\Documents\PRIVATE\SensuCarens\website_sozai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CED7B95-8A45-4654-B7F2-E950E1EBD205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9338E431-24D1-4E4C-8109-EC4BB21A1652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="410" yWindow="120" windowWidth="18640" windowHeight="8170" xr2:uid="{342DAAEC-2FF0-46AB-8AEF-D541469D4F9E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{342DAAEC-2FF0-46AB-8AEF-D541469D4F9E}"/>
   </bookViews>
   <sheets>
     <sheet name="profile" sheetId="1" r:id="rId1"/>
@@ -73,15 +73,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ミニアルバム「SensuCarens」リリース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Jun</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミニアルバム「Pink into Pink」リリース</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -106,21 +98,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ミニアルバム「ambiguous」リリース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Sep</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Dr.晃次郎が加入</t>
-    <rPh sb="3" eb="6">
-      <t>コウジロウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カニュウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -137,6 +115,28 @@
     <t>現在</t>
     <rPh sb="0" eb="2">
       <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>single「Pink into Pink」release</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>single「SensuCarens」release</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EP「ambiguous」releace</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dr. 晃次郎が加入</t>
+    <rPh sb="4" eb="7">
+      <t>コウジロウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カニュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -560,10 +560,10 @@
         <v>2010</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -571,10 +571,10 @@
         <v>2014</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -582,10 +582,10 @@
         <v>2020</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -593,18 +593,18 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
